--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137032665</v>
       </c>
       <c r="B2" t="n">
-        <v>81312</v>
+        <v>81314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,45 +792,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137032703</v>
+        <v>137033758</v>
       </c>
       <c r="B3" t="n">
-        <v>83450</v>
+        <v>81314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>1555</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gul pysslinglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelopsis flaveola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Arnold</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>N om Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490804</v>
+        <v>490847</v>
       </c>
       <c r="R3" t="n">
-        <v>6667512</v>
+        <v>6667606</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,54 +871,65 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>stambas på hundraårig gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Janolof Hermansson, Lars Ström, Ulf Svensson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032703</t>
+          <t>https://artportalen.se/Sighting/137033758</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137032711</v>
+        <v>137032703</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>83452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +937,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490800</v>
+        <v>490804</v>
       </c>
       <c r="R4" t="n">
-        <v>6667524</v>
+        <v>6667512</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,13 +1032,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032711</t>
+          <t>https://artportalen.se/Sighting/137032703</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137032718</v>
+        <v>137032711</v>
       </c>
       <c r="B5" t="n">
         <v>58005</v>
@@ -1056,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490868</v>
+        <v>490800</v>
       </c>
       <c r="R5" t="n">
-        <v>6667586</v>
+        <v>6667524</v>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1118,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spår</t>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,38 +1149,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032718</t>
+          <t>https://artportalen.se/Sighting/137032711</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137032677</v>
+        <v>137032718</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1190,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490925</v>
+        <v>490868</v>
       </c>
       <c r="R6" t="n">
-        <v>6667543</v>
+        <v>6667586</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1235,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1266,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032677</t>
+          <t>https://artportalen.se/Sighting/137032718</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137032709</v>
+        <v>137032677</v>
       </c>
       <c r="B7" t="n">
-        <v>58164</v>
+        <v>58169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,13 +1307,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490797</v>
+        <v>490925</v>
       </c>
       <c r="R7" t="n">
-        <v>6667521</v>
+        <v>6667543</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,16 +1378,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032709</t>
+          <t>https://artportalen.se/Sighting/137032677</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137032667</v>
+        <v>137032709</v>
       </c>
       <c r="B8" t="n">
-        <v>111338</v>
+        <v>58164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1395,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220240</v>
+        <v>103023</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490884</v>
+        <v>490797</v>
       </c>
       <c r="R8" t="n">
-        <v>6667561</v>
+        <v>6667521</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,6 +1489,118 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137032709</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137032667</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111340</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Abborrberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490884</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6667561</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137032667</t>
         </is>
@@ -1481,6 +1615,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137032665</v>
+        <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>81314</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1555</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul pysslinglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelopsis flaveola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Arnold</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>N om Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490848</v>
+        <v>490854</v>
       </c>
       <c r="R2" t="n">
-        <v>6667615</v>
+        <v>6667579</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,51 +751,72 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rik vegetation bl.a. vass</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Janolof Hermansson, Lars Ström, Sture Lindstrand, Ulf Svensson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032665</t>
+          <t>https://artportalen.se/Sighting/137078589</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137033758</v>
+        <v>137032665</v>
       </c>
       <c r="B3" t="n">
         <v>81314</v>
@@ -820,28 +844,17 @@
           <t>Arnold</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N om Abborrtjärnen, Dlr</t>
+          <t>Abborrberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490847</v>
+        <v>490848</v>
       </c>
       <c r="R3" t="n">
-        <v>6667606</v>
+        <v>6667615</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,100 +884,100 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>stambas på hundraårig gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Lars Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Lars Ström, Ulf Svensson, Bengt Lundborg</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137033758</t>
+          <t>https://artportalen.se/Sighting/137032665</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137032703</v>
+        <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>83452</v>
+        <v>81314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>1555</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gul pysslinglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelopsis flaveola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Arnold</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>N om Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490804</v>
+        <v>490847</v>
       </c>
       <c r="R4" t="n">
-        <v>6667512</v>
+        <v>6667606</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,54 +1007,65 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>stambas på hundraårig gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Janolof Hermansson, Lars Ström, Ulf Svensson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032703</t>
+          <t>https://artportalen.se/Sighting/137033758</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137032711</v>
+        <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1073,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>N om Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490800</v>
+        <v>490854</v>
       </c>
       <c r="R5" t="n">
-        <v>6667524</v>
+        <v>6667579</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,59 +1133,75 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammalt spår</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>rik vegetation bl.a. vass</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Janolof Hermansson, Lars Ström, Sture Lindstrand, Ulf Svensson, Bengt Lundborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032711</t>
+          <t>https://artportalen.se/Sighting/137078582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137032718</v>
+        <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>83452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1209,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,13 +1233,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490868</v>
+        <v>490804</v>
       </c>
       <c r="R6" t="n">
-        <v>6667586</v>
+        <v>6667512</v>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,12 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,38 +1304,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032718</t>
+          <t>https://artportalen.se/Sighting/137032703</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137032677</v>
+        <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,13 +1345,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490925</v>
+        <v>490800</v>
       </c>
       <c r="R7" t="n">
-        <v>6667543</v>
+        <v>6667524</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,7 +1380,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1390,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammalt spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,16 +1421,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032677</t>
+          <t>https://artportalen.se/Sighting/137032711</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137032709</v>
+        <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,16 +1438,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1419,13 +1462,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490797</v>
+        <v>490868</v>
       </c>
       <c r="R8" t="n">
-        <v>6667521</v>
+        <v>6667586</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1507,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,38 +1538,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032709</t>
+          <t>https://artportalen.se/Sighting/137032718</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137032667</v>
+        <v>137032677</v>
       </c>
       <c r="B9" t="n">
-        <v>111340</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220240</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1531,10 +1579,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490884</v>
+        <v>490925</v>
       </c>
       <c r="R9" t="n">
-        <v>6667561</v>
+        <v>6667543</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,6 +1649,230 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137032677</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137032709</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Abborrberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490797</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6667521</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137032709</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137032667</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111340</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Abborrberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490884</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6667561</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Ström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137032667</t>
         </is>
@@ -1616,6 +1888,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81314</v>
+        <v>81315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81314</v>
+        <v>81315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1544,48 +1544,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137032677</v>
+        <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100110</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490925</v>
+        <v>490871</v>
       </c>
       <c r="R9" t="n">
-        <v>6667543</v>
+        <v>6667516</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,22 +1614,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,27 +1634,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032677</t>
+          <t>https://artportalen.se/Sighting/137096774</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137032709</v>
+        <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>58164</v>
+        <v>57186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,16 +1662,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103023</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1685,19 +1680,29 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Abborrberg, Dlr</t>
+          <t>Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490797</v>
+        <v>490761</v>
       </c>
       <c r="R10" t="n">
-        <v>6667521</v>
+        <v>6667484</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,22 +1726,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:12</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Svarar på min lockpipa Utmärkt miljö för arten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1751,49 +1751,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Ström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137032709</t>
+          <t>https://artportalen.se/Sighting/137097114</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137032667</v>
+        <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>111340</v>
+        <v>58169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220240</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490884</v>
+        <v>490925</v>
       </c>
       <c r="R11" t="n">
-        <v>6667561</v>
+        <v>6667543</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,6 +1873,230 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137032677</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137032709</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abborrberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490797</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6667521</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Ström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137032709</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137032667</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111341</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abborrberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490884</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6667561</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Ström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137032667</t>
         </is>
@@ -1890,6 +2114,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81315</v>
+        <v>81317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81315</v>
+        <v>81317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81317</v>
+        <v>81315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81317</v>
+        <v>81315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81315</v>
+        <v>81328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81315</v>
+        <v>81328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81328</v>
+        <v>81330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81328</v>
+        <v>81330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -1573,11 +1573,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Dlr</t>
@@ -1680,16 +1676,8 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Abborrtjärnen, Dlr</t>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81330</v>
+        <v>81340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81330</v>
+        <v>81340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81340</v>
+        <v>81343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81340</v>
+        <v>81343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81343</v>
+        <v>81348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81343</v>
+        <v>81348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
+          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Ström, Sture Lindstrand, Bengt Lundborg, Ulf Svensson, Janolof Hermansson</t>
+          <t>Lars Ström, Janolof Hermansson, Ulf Svensson, Bengt Lundborg, Sture Lindstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81348</v>
+        <v>81359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81348</v>
+        <v>81359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81359</v>
+        <v>81360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81359</v>
+        <v>81360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81360</v>
+        <v>81362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81360</v>
+        <v>81362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37350-2026 artfynd.xlsx
+++ b/artfynd/A 37350-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137078589</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137032665</v>
       </c>
       <c r="B3" t="n">
-        <v>81362</v>
+        <v>81366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137033758</v>
       </c>
       <c r="B4" t="n">
-        <v>81362</v>
+        <v>81366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>137078582</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>137032703</v>
       </c>
       <c r="B6" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>137032711</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>137032718</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>137096774</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137097114</v>
       </c>
       <c r="B10" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137032677</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137032709</v>
       </c>
       <c r="B12" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>137032667</v>
       </c>
       <c r="B13" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
